--- a/Results/MOVICS_baseline/MOVICS_TCGA_RNAseq-CNV-Methylation-miRNA-SNPs_eval_on_transNEO_clusterings.xlsx
+++ b/Results/MOVICS_baseline/MOVICS_TCGA_RNAseq-CNV-Methylation-miRNA-SNPs_eval_on_transNEO_clusterings.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="627">
   <si>
     <t xml:space="preserve">Sample.ID</t>
   </si>
@@ -20,1936 +20,1879 @@
     <t xml:space="preserve">Cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">TCGA-3C-AAAU-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-3C-AALI-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-3C-AALJ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-3C-AALK-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-5L-AAT0-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-5L-AAT1-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-5T-A9QA-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A1-A0SB-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A1-A0SE-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A1-A0SF-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A1-A0SG-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A1-A0SH-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A1-A0SI-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A1-A0SJ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A1-A0SK-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A1-A0SO-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A1-A0SP-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A1-A0SQ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A04R-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0CR-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0CT-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0EN-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0EP-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0EU-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0ST-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0SU-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0SV-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0SW-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0SX-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0SY-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0T0-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0T1-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0T2-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0T4-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0T5-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0T6-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0T7-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0YC-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0YD-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0YF-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0YG-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0YH-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0YI-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0YK-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0YL-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0YM-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0YT-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A1FV-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A1FW-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A1FX-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A1FZ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A1G0-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A1G1-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A1G4-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A1G6-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A259-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A25A-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A25B-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A25C-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A25D-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A25E-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A25F-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A3KD-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A3XU-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A3XW-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A3Y0-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A4RW-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A4S1-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A4S2-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A4S3-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A0D9-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A13D-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A13E-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A13F-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A13G-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A26E-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A26F-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A26G-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A26H-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A26I-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A26J-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A4SC-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A4SE-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A4SF-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A56D-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A5ZV-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A5ZW-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A5ZX-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A6VV-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A6VW-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A6VX-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A6VY-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A8-A075-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A8-A08O-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A8-A0A6-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A8-A0AD-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A23C-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A23E-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A23G-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A23H-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A2B8-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A2BK-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A2BM-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A2FB-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A2FF-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A2FG-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A2FO-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A2QH-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A3OD-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A3QQ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A3W7-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A3YI-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A4ZE-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A5EH-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A5XS-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A5XU-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A62X-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A62Y-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A6IV-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A6IW-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A6IX-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A6NO-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A7VB-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A7VC-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A8OP-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A8OQ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A8OR-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A8OS-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AN-A0XN-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AN-A0XO-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AN-A0XP-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AN-A0XR-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AN-A0XS-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AN-A0XU-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AN-A0XV-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AN-A0XW-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AO-A03L-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AO-A0JA-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AO-A0JB-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AO-A0JC-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AO-A0JD-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AO-A0JE-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AO-A0JF-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AO-A0JG-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AO-A0JI-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AO-A0JJ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AO-A0JM-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AO-A124-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AO-A128-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AO-A1KP-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AO-A1KR-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AO-A1KS-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AO-A1KT-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AQ-A04H-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AQ-A0Y5-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AQ-A1H2-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AQ-A1H3-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AQ-A54N-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AQ-A7U7-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A0TP-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A0TQ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A0TR-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A0TT-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A0TV-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A0TX-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A0TZ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A0U2-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A0U3-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A1AI-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A1AJ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A1AK-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A1AL-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A1AN-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A1AO-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A1AP-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A1AQ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A1AR-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A1AS-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A1AU-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A1AW-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A1AX-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A1AY-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A24H-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A24K-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A24L-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A24M-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A24N-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A24O-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A24P-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A24Q-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A24R-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A24S-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A24T-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A24U-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A24V-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A24W-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A24X-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A24Z-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A250-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A251-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A252-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A254-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A255-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A256-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A2LE-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A2LH-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A2LK-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A2LL-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A2LM-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A2LN-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A2LO-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A2LQ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A2LR-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A5QM-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A5QN-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A5QP-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A5QQ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0IK-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0RE-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0RG-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0RI-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0RL-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0RM-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0RN-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0RO-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0RP-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0RS-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0RT-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0RU-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0RV-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0WT-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0WV-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0WW-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0WX-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0WY-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0WZ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0X4-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0X5-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A1KC-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A1KF-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A1KI-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A1KN-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A2IU-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A401-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A409-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A40C-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0AU-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0AW-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0AZ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0B3-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0B5-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0B6-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0B8-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0B9-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0BA-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0BF-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0BJ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0BM-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0BT-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0BZ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0C0-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0C3-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0DG-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0DH-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0DI-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0DK-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0DP-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0DQ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0DS-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0DV-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0E0-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0E1-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0E2-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0GY-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0GZ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0H0-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0H3-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0H6-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0H7-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0H9-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0HA-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0HB-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0HF-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0HI-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0HK-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0HN-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0HP-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0HX-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0HY-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0RX-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0W3-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0W4-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0W5-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0WA-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1EN-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1EO-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1ES-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1ET-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1EU-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1EV-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1EW-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1EX-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1EY-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1F0-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1F2-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1F5-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1F6-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1F8-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1FC-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1FE-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1FG-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1FH-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1FJ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1FL-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1FM-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1FN-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1FR-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1FU-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A201-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A202-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A203-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A204-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A208-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A209-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A28Q-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A2L8-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A42U-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A42V-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A5IZ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A5J0-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A6R8-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A6R9-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A8FY-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A8FZ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A8G0-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-AB28-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A1HE-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A1HF-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A1HG-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A1HI-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A1HJ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A1HK-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A1HL-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A1HM-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A1HN-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A1HO-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A26V-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A26W-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A26X-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A26Y-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A26Z-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A273-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A274-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A275-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A278-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A27A-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A27B-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A8HP-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A8HQ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A8HR-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1J8-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1J9-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1JA-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1JB-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1JC-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1JD-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1JE-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1JF-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1JG-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1JH-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1JI-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1JJ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1JK-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1JL-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1JN-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1JP-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1JS-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1JT-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1JU-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1X5-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1X6-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1X7-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1X8-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1X9-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1XA-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1XB-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1XC-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1XF-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1XG-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1XJ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1XK-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1XL-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1XM-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1XO-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1XQ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1XR-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1XT-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1XU-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1XV-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1XW-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1XY-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1XZ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1Y0-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1Y1-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1Y2-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1Y3-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A27E-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A27F-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A27G-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A27H-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A27I-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A27K-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A27L-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A27M-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A27P-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A27R-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A27T-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A27V-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A27W-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A3Z6-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A4Z1-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A73U-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A73W-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A73X-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A10C-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A14N-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A15I-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A15J-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A15K-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1AZ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1B0-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1B1-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1B4-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1B5-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1B6-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1BC-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1BD-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1IE-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1IF-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1IG-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1IH-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1II-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1IJ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1IK-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1IN-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1IO-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1IU-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1L6-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1L7-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1L8-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1L9-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1LA-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1LB-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1LG-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1LH-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1LK-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1LL-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A2P5-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A56Z-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A570-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A572-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A573-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A574-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A576-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A9RU-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1N3-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1N4-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1N5-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1N8-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1N9-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1NA-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1ND-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1NE-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1NF-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1NG-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1NH-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1NI-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1QZ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1R0-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1R2-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1R3-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1R4-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1R5-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1R6-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1R7-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1RA-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1RB-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1RC-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1RD-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1RE-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1RF-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1RG-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1RH-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1RI-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A226-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A227-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A228-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A229-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A22A-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A22B-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A22D-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A22E-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A22G-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A22H-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A243-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A244-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A245-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A247-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A248-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A24A-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A295-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A2JS-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A2JT-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A3X8-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A54Y-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A5FK-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A5FL-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A5UO-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A6HE-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1IW-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1IX-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1IY-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1IZ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1J1-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1J2-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1J3-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1J5-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1J6-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1OV-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1OX-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1OY-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1OZ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1P0-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1P1-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1P3-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1P4-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1P5-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1P6-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1P7-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1P8-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1PA-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1PB-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1PE-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1PG-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1PH-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A2FS-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A2FV-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A2FW-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A6S9-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A6SB-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A6SC-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A6SD-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GI-A2C8-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A2D9-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A2DA-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A2DB-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A2DC-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A2DD-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A2DF-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A2DH-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A2DI-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A2DK-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A2DL-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A2DM-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A2DN-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A2DO-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A3NW-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A3XG-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A3XL-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A5PV-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A5PX-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-HN-A2NL-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-HN-A2OB-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LD-A66U-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LD-A74U-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LD-A7W6-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LD-A9QF-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LL-A50Y-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LL-A5YL-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LL-A5YM-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LL-A5YN-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LL-A5YO-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LL-A5YP-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LL-A6FP-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LL-A6FQ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LL-A6FR-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LL-A73Y-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LL-A73Z-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LL-A740-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LL-A7SZ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LL-A7T0-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LL-A8F5-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LL-A9Q3-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OK-A5Q2-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A5D6-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A5D7-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A5D8-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A5DA-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A5RU-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A5RV-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A5RW-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A5RX-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A5RY-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A5RZ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A5S0-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A66H-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A66I-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A66J-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A66K-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A66L-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A66N-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A66O-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A66P-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A6VO-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A6VQ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A6VR-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A97C-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-PE-A5DC-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-PE-A5DD-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-PE-A5DE-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-PL-A8LV-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-PL-A8LX-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-PL-A8LY-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-PL-A8LZ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-S3-A6ZF-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-S3-A6ZG-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-S3-A6ZH-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-S3-AA0Z-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-S3-AA10-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-S3-AA11-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-S3-AA12-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-S3-AA14-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-S3-AA15-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-S3-AA17-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-UL-AAZ6-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-UU-A93S-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-V7-A7HQ-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-W8-A86G-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-WT-AB41-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-WT-AB44-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-XX-A899-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-XX-A89A-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-Z7-A8R5-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-Z7-A8R6-01</t>
+    <t xml:space="preserve">TCGA-AQ-A0Y5-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A2FW-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A274-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0IK-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1L7-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A247-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0WV-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0SV-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0DI-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A1-A0SB-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A2FG-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AQ-A7U7-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GM-A2DF-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1EN-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1Y2-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1B1-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0WX-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A23E-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A278-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A3W7-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1PH-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A6R8-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A27W-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A0U2-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0H9-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-W8-A86G-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A1-A0SG-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A1HK-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0B6-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GM-A2DK-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A5UO-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A24H-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0RO-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A15I-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A2BK-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-Z7-A8R5-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0RG-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A14N-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1B0-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A4S2-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A24A-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-4H-AAAK-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1EW-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A26J-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A24W-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LL-A5YP-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1II-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-HN-A2NL-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A26E-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1IU-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1N3-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A5IZ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A3XU-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0YC-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AO-A0JB-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AN-A0XU-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1EY-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-S3-AA12-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1IE-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1XG-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0E0-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A24L-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-S3-AA10-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0BT-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A66O-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A1AJ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A244-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A5RV-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A22H-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A0D9-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A3Y0-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1EU-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1P5-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1OY-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1XT-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0RL-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A24P-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A256-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A243-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1LH-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1PG-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0HB-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GM-A3NW-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1JN-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A1G1-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A25E-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A2L8-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GM-A2DM-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A8-A075-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0WA-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A25C-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0GY-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A23H-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A42V-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AO-A0JG-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0RP-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A9RU-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A401-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0DH-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-S3-AA0Z-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1LA-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A229-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1Y0-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1OZ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-PL-A8LZ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-S3-AA14-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LL-A6FQ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1RB-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A3X8-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1XM-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AN-A0XS-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0AU-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1XQ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1OX-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LD-A66U-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A1AY-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1IY-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A2LL-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1XU-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1R4-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A27R-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A22G-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1JJ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A4RW-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0HA-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1NA-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1XB-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-3C-AALJ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A24M-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0BM-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A6HE-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1FE-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AO-A128-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0RM-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1Y3-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A5J0-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1NF-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A0U3-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GM-A5PV-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A1-A0SP-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1F8-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1QZ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A2LN-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A1AS-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A209-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0DP-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1IJ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A574-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1XC-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-3C-AALK-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A6IV-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A3KD-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1L6-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A54Y-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A24S-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0SY-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A97C-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1B5-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A26X-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A5QM-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A8HQ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1N4-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A13G-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0H3-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1JE-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GM-A2D9-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A24O-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-V7-A7HQ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GM-A3XL-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A2FB-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0T1-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1JC-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1XY-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A1HF-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0DQ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AN-A0XT-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A1HJ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A2B8-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LL-A7SZ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0WZ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0RE-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-AB28-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A1-A0SQ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0YD-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1P3-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1RE-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A1-A0SJ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0RN-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A5ZW-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1JD-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1FL-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A27F-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LL-A6FR-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A0TT-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A1-A0SI-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0SX-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0B3-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LD-A7W5-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-S3-A6ZG-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A250-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A22E-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A6NO-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A8HP-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A8OS-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A27N-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A8HR-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0DG-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1B4-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GM-A2DC-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A226-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1JB-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A3Z6-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A26H-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1IK-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A5ZX-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AO-A0JM-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A2LM-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A259-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0X5-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A28Q-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1XL-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0BS-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A1KI-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A1-A0SN-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0W5-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0CR-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AO-A124-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AO-A0JD-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1JG-01B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0BZ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A1-A0SH-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0WT-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A26F-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A255-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-UL-AAZ6-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A1FW-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AO-A1KS-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0YT-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A62X-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A1-A0SK-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1IF-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1XA-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-PL-A8LY-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A27E-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0RU-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1FG-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LL-A7T0-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A4SE-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A24R-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LD-A7W6-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A5D8-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A27H-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1BD-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A1KN-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A208-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1J3-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1FM-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1EX-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0C3-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A1AN-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0T7-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A5S0-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A5RX-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-UU-A93S-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AQ-A54N-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GM-A2DH-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A273-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A8G0-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-WT-AB44-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0B9-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1RC-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0EN-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1L9-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A8-A08O-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A56Z-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1JT-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1X7-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A570-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1XJ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A1FV-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0HI-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A22D-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LL-A50Y-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0RS-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0T0-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1XK-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A1AU-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1X9-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1Y1-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1RD-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A254-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A27L-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1J8-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1RH-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0RI-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A573-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A0TV-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A1-A0SF-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1PA-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-PE-A5DE-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A1HM-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A5DA-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A24N-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A24U-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A202-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1J6-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A24V-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A8OQ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1N8-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0H6-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AN-A0XV-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0YL-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1JU-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A1FX-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A2LO-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A27V-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AO-A0JF-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A2JT-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A203-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A25A-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A1KF-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1AZ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LL-A73Y-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GM-A5PX-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A1AX-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A66N-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1L8-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A2P5-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GM-A2DL-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A56D-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AN-A0XN-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A5EH-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A1-A0SE-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1JH-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A27P-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A5FL-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0SU-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-S3-A6ZF-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0HP-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A66P-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-XX-A899-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AO-A0JJ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AQ-A04H-01B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A4S1-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-S3-AA17-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1X8-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A27A-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1RG-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0W3-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1NE-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0YF-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1OV-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A8-A0AD-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1NH-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1JL-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1PB-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A26V-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LL-A5YM-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A2FO-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A73W-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1X5-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1J1-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1LG-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A1AR-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0WW-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A27B-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1P1-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A23G-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A3OD-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1R0-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A0TX-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A0TR-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A5D6-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A6VY-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1N5-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A6IW-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0DS-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1P0-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A40C-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-PL-A8LX-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0EU-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A295-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A245-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A26W-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AQ-A1H3-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0HY-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A8-A0A6-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1RA-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1ET-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0BC-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A227-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0BA-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0E2-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A2JS-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0HK-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A2LK-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-5T-A9QA-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A73X-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0X4-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A5QQ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AO-A0JA-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0HX-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A25D-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A201-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-5L-AAT0-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-WT-AB41-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A5QP-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A13D-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A23C-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0T4-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A27M-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-Z7-A8R6-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A66L-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A1HE-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-PE-A5DD-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GM-A2DD-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A26I-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A04R-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1PE-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1IL-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1XW-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A0TP-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A2FV-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1FJ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AN-A0XR-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1IH-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-S3-A6ZH-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LL-A5YN-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1P6-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A576-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1ND-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0DK-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A1G4-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1FU-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GM-A2DA-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AQ-A1H2-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0YG-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1IZ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0AW-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1NI-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1RF-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A0TZ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A5D7-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1N9-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AO-A1KR-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A5RU-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A4Z1-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A1FZ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1FC-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A1AI-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A2IU-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A1AQ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A6VW-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0SW-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1EV-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A4S3-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A2LQ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A22B-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A228-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AN-A0XW-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0YM-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1XV-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A6VQ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-3C-AAAU-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1JP-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LL-A9Q3-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A252-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A2FF-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A66K-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A4ZE-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A22A-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A6VV-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A27G-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A1G0-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1J2-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A1HN-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A2BM-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0RT-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1IN-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A6VX-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A27K-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A24K-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0H0-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0BF-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A26G-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1F5-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1RI-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0B5-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1P8-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0GZ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A1AL-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1F6-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0WY-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0T2-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A27I-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A6S9-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1X6-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-XX-A89A-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1IX-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AN-A0XP-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A4SF-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LL-A740-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1J5-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1LB-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A6SB-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1R5-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1ES-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0YI-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A6IX-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A10C-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1JA-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1XO-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1F2-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GM-A2DI-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AO-A03L-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1P7-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A5RW-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LL-A73Z-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A1HL-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GM-A2DB-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A204-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0W4-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A5QN-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A62Y-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0T6-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1XZ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1LL-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A7VC-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A13F-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A15J-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0H7-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1F0-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LL-A5YL-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A3YI-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A8FZ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1LK-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AO-A1KT-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1P4-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A409-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A248-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0AZ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A15K-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AN-A0XO-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A24Z-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1NG-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A1AW-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1JK-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A7VB-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-3C-AALI-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A2FS-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1J9-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1BC-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0BJ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A5XS-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A6VR-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A26Z-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1JF-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1FN-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A1HG-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A27T-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1JS-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1R7-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0YH-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A5ZV-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A26Y-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A66H-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1JI-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A5RZ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A6R9-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1EO-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GM-A2DN-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A0TQ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A8FY-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1IW-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A13E-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1XF-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A8OR-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A251-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A24X-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1R3-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0RV-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OK-A5Q2-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1R6-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A275-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LL-A8F5-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0YK-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A1AP-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A1AK-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A66J-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A73U-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A5XU-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A6SC-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A66I-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0DV-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0CT-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LD-A74U-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0T5-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AO-A1KP-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AO-A0JE-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A2LH-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A6VO-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-HN-A2OB-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A1AO-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0E1-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A2QH-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A6SD-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-PL-A8LV-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A5RY-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A8OP-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LL-A6FP-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GI-A2C8-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A2LR-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AO-A0JI-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A1HO-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A1HI-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0C0-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A1KC-01B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GM-A2DO-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A24Q-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1XR-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1R2-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1IG-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A2LE-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1IO-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-S3-AA11-01A</t>
   </si>
 </sst>
 </file>
@@ -2299,7 +2242,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -2315,7 +2258,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2323,7 +2266,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -2355,7 +2298,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -2363,7 +2306,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -2371,7 +2314,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -2379,7 +2322,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -2387,7 +2330,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -2419,7 +2362,7 @@
         <v>18</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -2443,7 +2386,7 @@
         <v>21</v>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -2459,7 +2402,7 @@
         <v>23</v>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -2499,7 +2442,7 @@
         <v>28</v>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2515,7 +2458,7 @@
         <v>30</v>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2523,7 +2466,7 @@
         <v>31</v>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2539,7 +2482,7 @@
         <v>33</v>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2547,7 +2490,7 @@
         <v>34</v>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2555,7 +2498,7 @@
         <v>35</v>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2579,7 +2522,7 @@
         <v>38</v>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2603,7 +2546,7 @@
         <v>41</v>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2611,7 +2554,7 @@
         <v>42</v>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2635,7 +2578,7 @@
         <v>45</v>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -2651,7 +2594,7 @@
         <v>47</v>
       </c>
       <c r="B47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -2659,7 +2602,7 @@
         <v>48</v>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -2667,7 +2610,7 @@
         <v>49</v>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -2675,7 +2618,7 @@
         <v>50</v>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -2683,7 +2626,7 @@
         <v>51</v>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -2691,7 +2634,7 @@
         <v>52</v>
       </c>
       <c r="B52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -2699,7 +2642,7 @@
         <v>53</v>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -2715,7 +2658,7 @@
         <v>55</v>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -2723,7 +2666,7 @@
         <v>56</v>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -2739,7 +2682,7 @@
         <v>58</v>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -2747,7 +2690,7 @@
         <v>59</v>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -2755,7 +2698,7 @@
         <v>60</v>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -2763,7 +2706,7 @@
         <v>61</v>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -2795,7 +2738,7 @@
         <v>65</v>
       </c>
       <c r="B65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -2811,7 +2754,7 @@
         <v>67</v>
       </c>
       <c r="B67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -2835,7 +2778,7 @@
         <v>70</v>
       </c>
       <c r="B70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -2851,7 +2794,7 @@
         <v>72</v>
       </c>
       <c r="B72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -2867,7 +2810,7 @@
         <v>74</v>
       </c>
       <c r="B74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -2883,7 +2826,7 @@
         <v>76</v>
       </c>
       <c r="B76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -2891,7 +2834,7 @@
         <v>77</v>
       </c>
       <c r="B77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -2907,7 +2850,7 @@
         <v>79</v>
       </c>
       <c r="B79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -2923,7 +2866,7 @@
         <v>81</v>
       </c>
       <c r="B81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -2931,7 +2874,7 @@
         <v>82</v>
       </c>
       <c r="B82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -2939,7 +2882,7 @@
         <v>83</v>
       </c>
       <c r="B83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -2947,7 +2890,7 @@
         <v>84</v>
       </c>
       <c r="B84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -2955,7 +2898,7 @@
         <v>85</v>
       </c>
       <c r="B85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -2979,7 +2922,7 @@
         <v>88</v>
       </c>
       <c r="B88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
@@ -2987,7 +2930,7 @@
         <v>89</v>
       </c>
       <c r="B89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
@@ -2995,7 +2938,7 @@
         <v>90</v>
       </c>
       <c r="B90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -3003,7 +2946,7 @@
         <v>91</v>
       </c>
       <c r="B91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -3011,7 +2954,7 @@
         <v>92</v>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -3019,7 +2962,7 @@
         <v>93</v>
       </c>
       <c r="B93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -3035,7 +2978,7 @@
         <v>95</v>
       </c>
       <c r="B95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
@@ -3043,7 +2986,7 @@
         <v>96</v>
       </c>
       <c r="B96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
@@ -3075,7 +3018,7 @@
         <v>100</v>
       </c>
       <c r="B100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
@@ -3083,7 +3026,7 @@
         <v>101</v>
       </c>
       <c r="B101" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
@@ -3091,7 +3034,7 @@
         <v>102</v>
       </c>
       <c r="B102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
@@ -3107,7 +3050,7 @@
         <v>104</v>
       </c>
       <c r="B104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
@@ -3131,7 +3074,7 @@
         <v>107</v>
       </c>
       <c r="B107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3147,7 +3090,7 @@
         <v>109</v>
       </c>
       <c r="B109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3163,7 +3106,7 @@
         <v>111</v>
       </c>
       <c r="B111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -3195,7 +3138,7 @@
         <v>115</v>
       </c>
       <c r="B115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
@@ -3203,7 +3146,7 @@
         <v>116</v>
       </c>
       <c r="B116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117">
@@ -3211,7 +3154,7 @@
         <v>117</v>
       </c>
       <c r="B117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
@@ -3227,7 +3170,7 @@
         <v>119</v>
       </c>
       <c r="B119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
@@ -3235,7 +3178,7 @@
         <v>120</v>
       </c>
       <c r="B120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
@@ -3243,7 +3186,7 @@
         <v>121</v>
       </c>
       <c r="B121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -3259,7 +3202,7 @@
         <v>123</v>
       </c>
       <c r="B123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124">
@@ -3283,7 +3226,7 @@
         <v>126</v>
       </c>
       <c r="B126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127">
@@ -3291,7 +3234,7 @@
         <v>127</v>
       </c>
       <c r="B127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
@@ -3299,7 +3242,7 @@
         <v>128</v>
       </c>
       <c r="B128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
@@ -3315,7 +3258,7 @@
         <v>130</v>
       </c>
       <c r="B130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
@@ -3323,7 +3266,7 @@
         <v>131</v>
       </c>
       <c r="B131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
@@ -3331,7 +3274,7 @@
         <v>132</v>
       </c>
       <c r="B132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
@@ -3347,7 +3290,7 @@
         <v>134</v>
       </c>
       <c r="B134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135">
@@ -3387,7 +3330,7 @@
         <v>139</v>
       </c>
       <c r="B139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140">
@@ -3411,7 +3354,7 @@
         <v>142</v>
       </c>
       <c r="B142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143">
@@ -3419,7 +3362,7 @@
         <v>143</v>
       </c>
       <c r="B143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144">
@@ -3427,7 +3370,7 @@
         <v>144</v>
       </c>
       <c r="B144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -3435,7 +3378,7 @@
         <v>145</v>
       </c>
       <c r="B145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
@@ -3459,7 +3402,7 @@
         <v>148</v>
       </c>
       <c r="B148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
@@ -3467,7 +3410,7 @@
         <v>149</v>
       </c>
       <c r="B149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -3483,7 +3426,7 @@
         <v>151</v>
       </c>
       <c r="B151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152">
@@ -3499,7 +3442,7 @@
         <v>153</v>
       </c>
       <c r="B153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154">
@@ -3507,7 +3450,7 @@
         <v>154</v>
       </c>
       <c r="B154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="155">
@@ -3515,7 +3458,7 @@
         <v>155</v>
       </c>
       <c r="B155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="156">
@@ -3531,7 +3474,7 @@
         <v>157</v>
       </c>
       <c r="B157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">
@@ -3539,7 +3482,7 @@
         <v>158</v>
       </c>
       <c r="B158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159">
@@ -3571,7 +3514,7 @@
         <v>162</v>
       </c>
       <c r="B162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -3579,7 +3522,7 @@
         <v>163</v>
       </c>
       <c r="B163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164">
@@ -3587,7 +3530,7 @@
         <v>164</v>
       </c>
       <c r="B164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165">
@@ -3595,7 +3538,7 @@
         <v>165</v>
       </c>
       <c r="B165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="166">
@@ -3611,7 +3554,7 @@
         <v>167</v>
       </c>
       <c r="B167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="168">
@@ -3619,7 +3562,7 @@
         <v>168</v>
       </c>
       <c r="B168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="169">
@@ -3627,7 +3570,7 @@
         <v>169</v>
       </c>
       <c r="B169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="170">
@@ -3659,7 +3602,7 @@
         <v>173</v>
       </c>
       <c r="B173" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -3675,7 +3618,7 @@
         <v>175</v>
       </c>
       <c r="B175" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176">
@@ -3683,7 +3626,7 @@
         <v>176</v>
       </c>
       <c r="B176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
@@ -3707,7 +3650,7 @@
         <v>179</v>
       </c>
       <c r="B179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180">
@@ -3723,7 +3666,7 @@
         <v>181</v>
       </c>
       <c r="B181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="182">
@@ -3747,7 +3690,7 @@
         <v>184</v>
       </c>
       <c r="B184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -3755,7 +3698,7 @@
         <v>185</v>
       </c>
       <c r="B185" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -3763,7 +3706,7 @@
         <v>186</v>
       </c>
       <c r="B186" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187">
@@ -3787,7 +3730,7 @@
         <v>189</v>
       </c>
       <c r="B189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="190">
@@ -3795,7 +3738,7 @@
         <v>190</v>
       </c>
       <c r="B190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="191">
@@ -3803,7 +3746,7 @@
         <v>191</v>
       </c>
       <c r="B191" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192">
@@ -3811,7 +3754,7 @@
         <v>192</v>
       </c>
       <c r="B192" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="193">
@@ -3843,7 +3786,7 @@
         <v>196</v>
       </c>
       <c r="B196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="197">
@@ -3851,7 +3794,7 @@
         <v>197</v>
       </c>
       <c r="B197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="198">
@@ -3859,7 +3802,7 @@
         <v>198</v>
       </c>
       <c r="B198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="199">
@@ -3883,7 +3826,7 @@
         <v>201</v>
       </c>
       <c r="B201" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="202">
@@ -3899,7 +3842,7 @@
         <v>203</v>
       </c>
       <c r="B203" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="204">
@@ -3907,7 +3850,7 @@
         <v>204</v>
       </c>
       <c r="B204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="205">
@@ -3923,7 +3866,7 @@
         <v>206</v>
       </c>
       <c r="B206" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="207">
@@ -3939,7 +3882,7 @@
         <v>208</v>
       </c>
       <c r="B208" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="209">
@@ -3947,7 +3890,7 @@
         <v>209</v>
       </c>
       <c r="B209" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="210">
@@ -3955,7 +3898,7 @@
         <v>210</v>
       </c>
       <c r="B210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="211">
@@ -3963,7 +3906,7 @@
         <v>211</v>
       </c>
       <c r="B211" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="212">
@@ -3971,7 +3914,7 @@
         <v>212</v>
       </c>
       <c r="B212" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="213">
@@ -3979,7 +3922,7 @@
         <v>213</v>
       </c>
       <c r="B213" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="214">
@@ -3995,7 +3938,7 @@
         <v>215</v>
       </c>
       <c r="B215" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="216">
@@ -4003,7 +3946,7 @@
         <v>216</v>
       </c>
       <c r="B216" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="217">
@@ -4043,7 +3986,7 @@
         <v>221</v>
       </c>
       <c r="B221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="222">
@@ -4059,7 +4002,7 @@
         <v>223</v>
       </c>
       <c r="B223" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="224">
@@ -4083,7 +4026,7 @@
         <v>226</v>
       </c>
       <c r="B226" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227">
@@ -4091,7 +4034,7 @@
         <v>227</v>
       </c>
       <c r="B227" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="228">
@@ -4099,7 +4042,7 @@
         <v>228</v>
       </c>
       <c r="B228" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229">
@@ -4115,7 +4058,7 @@
         <v>230</v>
       </c>
       <c r="B230" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231">
@@ -4131,7 +4074,7 @@
         <v>232</v>
       </c>
       <c r="B232" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="233">
@@ -4139,7 +4082,7 @@
         <v>233</v>
       </c>
       <c r="B233" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234">
@@ -4147,7 +4090,7 @@
         <v>234</v>
       </c>
       <c r="B234" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235">
@@ -4155,7 +4098,7 @@
         <v>235</v>
       </c>
       <c r="B235" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236">
@@ -4195,7 +4138,7 @@
         <v>240</v>
       </c>
       <c r="B240" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241">
@@ -4203,7 +4146,7 @@
         <v>241</v>
       </c>
       <c r="B241" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242">
@@ -4211,7 +4154,7 @@
         <v>242</v>
       </c>
       <c r="B242" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243">
@@ -4219,7 +4162,7 @@
         <v>243</v>
       </c>
       <c r="B243" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="244">
@@ -4227,7 +4170,7 @@
         <v>244</v>
       </c>
       <c r="B244" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="245">
@@ -4235,7 +4178,7 @@
         <v>245</v>
       </c>
       <c r="B245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="246">
@@ -4251,7 +4194,7 @@
         <v>247</v>
       </c>
       <c r="B247" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="248">
@@ -4267,7 +4210,7 @@
         <v>249</v>
       </c>
       <c r="B249" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250">
@@ -4291,7 +4234,7 @@
         <v>252</v>
       </c>
       <c r="B252" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="253">
@@ -4315,7 +4258,7 @@
         <v>255</v>
       </c>
       <c r="B255" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256">
@@ -4347,7 +4290,7 @@
         <v>259</v>
       </c>
       <c r="B259" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="260">
@@ -4355,7 +4298,7 @@
         <v>260</v>
       </c>
       <c r="B260" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="261">
@@ -4363,7 +4306,7 @@
         <v>261</v>
       </c>
       <c r="B261" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="262">
@@ -4387,7 +4330,7 @@
         <v>264</v>
       </c>
       <c r="B264" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="265">
@@ -4419,7 +4362,7 @@
         <v>268</v>
       </c>
       <c r="B268" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="269">
@@ -4427,7 +4370,7 @@
         <v>269</v>
       </c>
       <c r="B269" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="270">
@@ -4443,7 +4386,7 @@
         <v>271</v>
       </c>
       <c r="B271" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="272">
@@ -4451,7 +4394,7 @@
         <v>272</v>
       </c>
       <c r="B272" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273">
@@ -4459,7 +4402,7 @@
         <v>273</v>
       </c>
       <c r="B273" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="274">
@@ -4467,7 +4410,7 @@
         <v>274</v>
       </c>
       <c r="B274" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="275">
@@ -4475,7 +4418,7 @@
         <v>275</v>
       </c>
       <c r="B275" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="276">
@@ -4491,7 +4434,7 @@
         <v>277</v>
       </c>
       <c r="B277" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="278">
@@ -4499,7 +4442,7 @@
         <v>278</v>
       </c>
       <c r="B278" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="279">
@@ -4507,7 +4450,7 @@
         <v>279</v>
       </c>
       <c r="B279" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="280">
@@ -4523,7 +4466,7 @@
         <v>281</v>
       </c>
       <c r="B281" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="282">
@@ -4531,7 +4474,7 @@
         <v>282</v>
       </c>
       <c r="B282" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="283">
@@ -4547,7 +4490,7 @@
         <v>284</v>
       </c>
       <c r="B284" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="285">
@@ -4563,7 +4506,7 @@
         <v>286</v>
       </c>
       <c r="B286" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="287">
@@ -4579,7 +4522,7 @@
         <v>288</v>
       </c>
       <c r="B288" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="289">
@@ -4587,7 +4530,7 @@
         <v>289</v>
       </c>
       <c r="B289" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="290">
@@ -4603,7 +4546,7 @@
         <v>291</v>
       </c>
       <c r="B291" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="292">
@@ -4619,7 +4562,7 @@
         <v>293</v>
       </c>
       <c r="B293" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="294">
@@ -4627,7 +4570,7 @@
         <v>294</v>
       </c>
       <c r="B294" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="295">
@@ -4635,7 +4578,7 @@
         <v>295</v>
       </c>
       <c r="B295" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="296">
@@ -4643,7 +4586,7 @@
         <v>296</v>
       </c>
       <c r="B296" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="297">
@@ -4651,7 +4594,7 @@
         <v>297</v>
       </c>
       <c r="B297" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="298">
@@ -4675,7 +4618,7 @@
         <v>300</v>
       </c>
       <c r="B300" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301">
@@ -4699,7 +4642,7 @@
         <v>303</v>
       </c>
       <c r="B303" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304">
@@ -4707,7 +4650,7 @@
         <v>304</v>
       </c>
       <c r="B304" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="305">
@@ -4731,7 +4674,7 @@
         <v>307</v>
       </c>
       <c r="B307" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="308">
@@ -4739,7 +4682,7 @@
         <v>308</v>
       </c>
       <c r="B308" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="309">
@@ -4771,7 +4714,7 @@
         <v>312</v>
       </c>
       <c r="B312" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="313">
@@ -4779,7 +4722,7 @@
         <v>313</v>
       </c>
       <c r="B313" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="314">
@@ -4787,7 +4730,7 @@
         <v>314</v>
       </c>
       <c r="B314" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="315">
@@ -4795,7 +4738,7 @@
         <v>315</v>
       </c>
       <c r="B315" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="316">
@@ -4803,7 +4746,7 @@
         <v>316</v>
       </c>
       <c r="B316" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="317">
@@ -4819,7 +4762,7 @@
         <v>318</v>
       </c>
       <c r="B318" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="319">
@@ -4843,7 +4786,7 @@
         <v>321</v>
       </c>
       <c r="B321" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="322">
@@ -4851,7 +4794,7 @@
         <v>322</v>
       </c>
       <c r="B322" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="323">
@@ -4859,7 +4802,7 @@
         <v>323</v>
       </c>
       <c r="B323" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="324">
@@ -4875,7 +4818,7 @@
         <v>325</v>
       </c>
       <c r="B325" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="326">
@@ -4883,7 +4826,7 @@
         <v>326</v>
       </c>
       <c r="B326" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="327">
@@ -4923,7 +4866,7 @@
         <v>331</v>
       </c>
       <c r="B331" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -4939,7 +4882,7 @@
         <v>333</v>
       </c>
       <c r="B333" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
@@ -4947,7 +4890,7 @@
         <v>334</v>
       </c>
       <c r="B334" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="335">
@@ -4955,7 +4898,7 @@
         <v>335</v>
       </c>
       <c r="B335" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="336">
@@ -4963,7 +4906,7 @@
         <v>336</v>
       </c>
       <c r="B336" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="337">
@@ -4979,7 +4922,7 @@
         <v>338</v>
       </c>
       <c r="B338" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="339">
@@ -4987,7 +4930,7 @@
         <v>339</v>
       </c>
       <c r="B339" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="340">
@@ -4995,7 +4938,7 @@
         <v>340</v>
       </c>
       <c r="B340" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="341">
@@ -5003,7 +4946,7 @@
         <v>341</v>
       </c>
       <c r="B341" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="342">
@@ -5019,7 +4962,7 @@
         <v>343</v>
       </c>
       <c r="B343" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="344">
@@ -5051,7 +4994,7 @@
         <v>347</v>
       </c>
       <c r="B347" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="348">
@@ -5075,7 +5018,7 @@
         <v>350</v>
       </c>
       <c r="B350" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="351">
@@ -5091,7 +5034,7 @@
         <v>352</v>
       </c>
       <c r="B352" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="353">
@@ -5107,7 +5050,7 @@
         <v>354</v>
       </c>
       <c r="B354" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="355">
@@ -5115,7 +5058,7 @@
         <v>355</v>
       </c>
       <c r="B355" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356">
@@ -5131,7 +5074,7 @@
         <v>357</v>
       </c>
       <c r="B357" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="358">
@@ -5155,7 +5098,7 @@
         <v>360</v>
       </c>
       <c r="B360" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="361">
@@ -5163,7 +5106,7 @@
         <v>361</v>
       </c>
       <c r="B361" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="362">
@@ -5195,7 +5138,7 @@
         <v>365</v>
       </c>
       <c r="B365" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="366">
@@ -5203,7 +5146,7 @@
         <v>366</v>
       </c>
       <c r="B366" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="367">
@@ -5219,7 +5162,7 @@
         <v>368</v>
       </c>
       <c r="B368" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="369">
@@ -5243,7 +5186,7 @@
         <v>371</v>
       </c>
       <c r="B371" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="372">
@@ -5251,7 +5194,7 @@
         <v>372</v>
       </c>
       <c r="B372" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="373">
@@ -5283,7 +5226,7 @@
         <v>376</v>
       </c>
       <c r="B376" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="377">
@@ -5299,7 +5242,7 @@
         <v>378</v>
       </c>
       <c r="B378" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="379">
@@ -5307,7 +5250,7 @@
         <v>379</v>
       </c>
       <c r="B379" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="380">
@@ -5315,7 +5258,7 @@
         <v>380</v>
       </c>
       <c r="B380" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="381">
@@ -5347,7 +5290,7 @@
         <v>384</v>
       </c>
       <c r="B384" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="385">
@@ -5355,7 +5298,7 @@
         <v>385</v>
       </c>
       <c r="B385" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="386">
@@ -5363,7 +5306,7 @@
         <v>386</v>
       </c>
       <c r="B386" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="387">
@@ -5395,7 +5338,7 @@
         <v>390</v>
       </c>
       <c r="B390" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="391">
@@ -5419,7 +5362,7 @@
         <v>393</v>
       </c>
       <c r="B393" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="394">
@@ -5427,7 +5370,7 @@
         <v>394</v>
       </c>
       <c r="B394" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="395">
@@ -5459,7 +5402,7 @@
         <v>398</v>
       </c>
       <c r="B398" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="399">
@@ -5467,7 +5410,7 @@
         <v>399</v>
       </c>
       <c r="B399" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="400">
@@ -5475,7 +5418,7 @@
         <v>400</v>
       </c>
       <c r="B400" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="401">
@@ -5491,7 +5434,7 @@
         <v>402</v>
       </c>
       <c r="B402" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="403">
@@ -5507,7 +5450,7 @@
         <v>404</v>
       </c>
       <c r="B404" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="405">
@@ -5515,7 +5458,7 @@
         <v>405</v>
       </c>
       <c r="B405" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="406">
@@ -5523,7 +5466,7 @@
         <v>406</v>
       </c>
       <c r="B406" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="407">
@@ -5531,7 +5474,7 @@
         <v>407</v>
       </c>
       <c r="B407" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="408">
@@ -5539,7 +5482,7 @@
         <v>408</v>
       </c>
       <c r="B408" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="409">
@@ -5547,7 +5490,7 @@
         <v>409</v>
       </c>
       <c r="B409" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="410">
@@ -5555,7 +5498,7 @@
         <v>410</v>
       </c>
       <c r="B410" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="411">
@@ -5571,7 +5514,7 @@
         <v>412</v>
       </c>
       <c r="B412" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="413">
@@ -5579,7 +5522,7 @@
         <v>413</v>
       </c>
       <c r="B413" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="414">
@@ -5587,7 +5530,7 @@
         <v>414</v>
       </c>
       <c r="B414" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="415">
@@ -5603,7 +5546,7 @@
         <v>416</v>
       </c>
       <c r="B416" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="417">
@@ -5627,7 +5570,7 @@
         <v>419</v>
       </c>
       <c r="B419" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="420">
@@ -5635,7 +5578,7 @@
         <v>420</v>
       </c>
       <c r="B420" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="421">
@@ -5643,7 +5586,7 @@
         <v>421</v>
       </c>
       <c r="B421" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="422">
@@ -5651,7 +5594,7 @@
         <v>422</v>
       </c>
       <c r="B422" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="423">
@@ -5659,7 +5602,7 @@
         <v>423</v>
       </c>
       <c r="B423" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="424">
@@ -5675,7 +5618,7 @@
         <v>425</v>
       </c>
       <c r="B425" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="426">
@@ -5683,7 +5626,7 @@
         <v>426</v>
       </c>
       <c r="B426" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="427">
@@ -5691,7 +5634,7 @@
         <v>427</v>
       </c>
       <c r="B427" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="428">
@@ -5707,7 +5650,7 @@
         <v>429</v>
       </c>
       <c r="B429" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="430">
@@ -5715,7 +5658,7 @@
         <v>430</v>
       </c>
       <c r="B430" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="431">
@@ -5731,7 +5674,7 @@
         <v>432</v>
       </c>
       <c r="B432" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="433">
@@ -5739,7 +5682,7 @@
         <v>433</v>
       </c>
       <c r="B433" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="434">
@@ -5747,7 +5690,7 @@
         <v>434</v>
       </c>
       <c r="B434" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="435">
@@ -5771,7 +5714,7 @@
         <v>437</v>
       </c>
       <c r="B437" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="438">
@@ -5787,7 +5730,7 @@
         <v>439</v>
       </c>
       <c r="B439" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="440">
@@ -5827,7 +5770,7 @@
         <v>444</v>
       </c>
       <c r="B444" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="445">
@@ -5851,7 +5794,7 @@
         <v>447</v>
       </c>
       <c r="B447" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="448">
@@ -5859,7 +5802,7 @@
         <v>448</v>
       </c>
       <c r="B448" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="449">
@@ -5867,7 +5810,7 @@
         <v>449</v>
       </c>
       <c r="B449" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="450">
@@ -5875,7 +5818,7 @@
         <v>450</v>
       </c>
       <c r="B450" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="451">
@@ -5891,7 +5834,7 @@
         <v>452</v>
       </c>
       <c r="B452" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="453">
@@ -5899,7 +5842,7 @@
         <v>453</v>
       </c>
       <c r="B453" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="454">
@@ -5907,7 +5850,7 @@
         <v>454</v>
       </c>
       <c r="B454" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="455">
@@ -5923,7 +5866,7 @@
         <v>456</v>
       </c>
       <c r="B456" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="457">
@@ -5955,7 +5898,7 @@
         <v>460</v>
       </c>
       <c r="B460" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="461">
@@ -5963,7 +5906,7 @@
         <v>461</v>
       </c>
       <c r="B461" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="462">
@@ -5987,7 +5930,7 @@
         <v>464</v>
       </c>
       <c r="B464" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="465">
@@ -5995,7 +5938,7 @@
         <v>465</v>
       </c>
       <c r="B465" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="466">
@@ -6003,7 +5946,7 @@
         <v>466</v>
       </c>
       <c r="B466" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="467">
@@ -6011,7 +5954,7 @@
         <v>467</v>
       </c>
       <c r="B467" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="468">
@@ -6027,7 +5970,7 @@
         <v>469</v>
       </c>
       <c r="B469" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="470">
@@ -6035,7 +5978,7 @@
         <v>470</v>
       </c>
       <c r="B470" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="471">
@@ -6043,7 +5986,7 @@
         <v>471</v>
       </c>
       <c r="B471" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="472">
@@ -6051,7 +5994,7 @@
         <v>472</v>
       </c>
       <c r="B472" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="473">
@@ -6059,7 +6002,7 @@
         <v>473</v>
       </c>
       <c r="B473" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="474">
@@ -6067,7 +6010,7 @@
         <v>474</v>
       </c>
       <c r="B474" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="475">
@@ -6075,7 +6018,7 @@
         <v>475</v>
       </c>
       <c r="B475" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="476">
@@ -6083,7 +6026,7 @@
         <v>476</v>
       </c>
       <c r="B476" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="477">
@@ -6107,7 +6050,7 @@
         <v>479</v>
       </c>
       <c r="B479" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="480">
@@ -6131,7 +6074,7 @@
         <v>482</v>
       </c>
       <c r="B482" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="483">
@@ -6147,7 +6090,7 @@
         <v>484</v>
       </c>
       <c r="B484" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="485">
@@ -6155,7 +6098,7 @@
         <v>485</v>
       </c>
       <c r="B485" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="486">
@@ -6163,7 +6106,7 @@
         <v>486</v>
       </c>
       <c r="B486" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="487">
@@ -6171,7 +6114,7 @@
         <v>487</v>
       </c>
       <c r="B487" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="488">
@@ -6179,7 +6122,7 @@
         <v>488</v>
       </c>
       <c r="B488" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="489">
@@ -6187,7 +6130,7 @@
         <v>489</v>
       </c>
       <c r="B489" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="490">
@@ -6195,7 +6138,7 @@
         <v>490</v>
       </c>
       <c r="B490" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="491">
@@ -6203,7 +6146,7 @@
         <v>491</v>
       </c>
       <c r="B491" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="492">
@@ -6211,7 +6154,7 @@
         <v>492</v>
       </c>
       <c r="B492" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="493">
@@ -6227,7 +6170,7 @@
         <v>494</v>
       </c>
       <c r="B494" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="495">
@@ -6243,7 +6186,7 @@
         <v>496</v>
       </c>
       <c r="B496" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="497">
@@ -6251,7 +6194,7 @@
         <v>497</v>
       </c>
       <c r="B497" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="498">
@@ -6259,7 +6202,7 @@
         <v>498</v>
       </c>
       <c r="B498" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="499">
@@ -6275,7 +6218,7 @@
         <v>500</v>
       </c>
       <c r="B500" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="501">
@@ -6283,7 +6226,7 @@
         <v>501</v>
       </c>
       <c r="B501" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="502">
@@ -6291,7 +6234,7 @@
         <v>502</v>
       </c>
       <c r="B502" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="503">
@@ -6299,7 +6242,7 @@
         <v>503</v>
       </c>
       <c r="B503" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="504">
@@ -6307,7 +6250,7 @@
         <v>504</v>
       </c>
       <c r="B504" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="505">
@@ -6315,7 +6258,7 @@
         <v>505</v>
       </c>
       <c r="B505" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="506">
@@ -6323,7 +6266,7 @@
         <v>506</v>
       </c>
       <c r="B506" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="507">
@@ -6339,7 +6282,7 @@
         <v>508</v>
       </c>
       <c r="B508" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="509">
@@ -6347,7 +6290,7 @@
         <v>509</v>
       </c>
       <c r="B509" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="510">
@@ -6371,7 +6314,7 @@
         <v>512</v>
       </c>
       <c r="B512" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="513">
@@ -6379,7 +6322,7 @@
         <v>513</v>
       </c>
       <c r="B513" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="514">
@@ -6395,7 +6338,7 @@
         <v>515</v>
       </c>
       <c r="B515" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="516">
@@ -6411,7 +6354,7 @@
         <v>517</v>
       </c>
       <c r="B517" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="518">
@@ -6419,7 +6362,7 @@
         <v>518</v>
       </c>
       <c r="B518" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="519">
@@ -6427,7 +6370,7 @@
         <v>519</v>
       </c>
       <c r="B519" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="520">
@@ -6451,7 +6394,7 @@
         <v>522</v>
       </c>
       <c r="B522" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="523">
@@ -6459,7 +6402,7 @@
         <v>523</v>
       </c>
       <c r="B523" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="524">
@@ -6483,7 +6426,7 @@
         <v>526</v>
       </c>
       <c r="B526" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="527">
@@ -6507,7 +6450,7 @@
         <v>529</v>
       </c>
       <c r="B529" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="530">
@@ -6515,7 +6458,7 @@
         <v>530</v>
       </c>
       <c r="B530" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="531">
@@ -6523,7 +6466,7 @@
         <v>531</v>
       </c>
       <c r="B531" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="532">
@@ -6539,7 +6482,7 @@
         <v>533</v>
       </c>
       <c r="B533" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="534">
@@ -6547,7 +6490,7 @@
         <v>534</v>
       </c>
       <c r="B534" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="535">
@@ -6563,7 +6506,7 @@
         <v>536</v>
       </c>
       <c r="B536" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="537">
@@ -6571,7 +6514,7 @@
         <v>537</v>
       </c>
       <c r="B537" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="538">
@@ -6579,7 +6522,7 @@
         <v>538</v>
       </c>
       <c r="B538" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="539">
@@ -6595,7 +6538,7 @@
         <v>540</v>
       </c>
       <c r="B540" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="541">
@@ -6603,7 +6546,7 @@
         <v>541</v>
       </c>
       <c r="B541" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="542">
@@ -6611,7 +6554,7 @@
         <v>542</v>
       </c>
       <c r="B542" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="543">
@@ -6627,7 +6570,7 @@
         <v>544</v>
       </c>
       <c r="B544" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="545">
@@ -6651,7 +6594,7 @@
         <v>547</v>
       </c>
       <c r="B547" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="548">
@@ -6667,7 +6610,7 @@
         <v>549</v>
       </c>
       <c r="B549" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="550">
@@ -6691,7 +6634,7 @@
         <v>552</v>
       </c>
       <c r="B552" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="553">
@@ -6699,7 +6642,7 @@
         <v>553</v>
       </c>
       <c r="B553" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="554">
@@ -6715,7 +6658,7 @@
         <v>555</v>
       </c>
       <c r="B555" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="556">
@@ -6723,7 +6666,7 @@
         <v>556</v>
       </c>
       <c r="B556" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="557">
@@ -6731,7 +6674,7 @@
         <v>557</v>
       </c>
       <c r="B557" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="558">
@@ -6747,7 +6690,7 @@
         <v>559</v>
       </c>
       <c r="B559" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="560">
@@ -6755,7 +6698,7 @@
         <v>560</v>
       </c>
       <c r="B560" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="561">
@@ -6763,7 +6706,7 @@
         <v>561</v>
       </c>
       <c r="B561" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="562">
@@ -6771,7 +6714,7 @@
         <v>562</v>
       </c>
       <c r="B562" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="563">
@@ -6779,7 +6722,7 @@
         <v>563</v>
       </c>
       <c r="B563" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="564">
@@ -6795,7 +6738,7 @@
         <v>565</v>
       </c>
       <c r="B565" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="566">
@@ -6811,7 +6754,7 @@
         <v>567</v>
       </c>
       <c r="B567" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="568">
@@ -6819,7 +6762,7 @@
         <v>568</v>
       </c>
       <c r="B568" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="569">
@@ -6851,7 +6794,7 @@
         <v>572</v>
       </c>
       <c r="B572" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="573">
@@ -6859,7 +6802,7 @@
         <v>573</v>
       </c>
       <c r="B573" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="574">
@@ -6867,7 +6810,7 @@
         <v>574</v>
       </c>
       <c r="B574" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="575">
@@ -6875,7 +6818,7 @@
         <v>575</v>
       </c>
       <c r="B575" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="576">
@@ -6915,7 +6858,7 @@
         <v>580</v>
       </c>
       <c r="B580" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="581">
@@ -6947,7 +6890,7 @@
         <v>584</v>
       </c>
       <c r="B584" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="585">
@@ -6955,7 +6898,7 @@
         <v>585</v>
       </c>
       <c r="B585" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="586">
@@ -6995,7 +6938,7 @@
         <v>590</v>
       </c>
       <c r="B590" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="591">
@@ -7003,7 +6946,7 @@
         <v>591</v>
       </c>
       <c r="B591" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="592">
@@ -7011,7 +6954,7 @@
         <v>592</v>
       </c>
       <c r="B592" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="593">
@@ -7035,7 +6978,7 @@
         <v>595</v>
       </c>
       <c r="B595" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="596">
@@ -7059,7 +7002,7 @@
         <v>598</v>
       </c>
       <c r="B598" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="599">
@@ -7067,7 +7010,7 @@
         <v>599</v>
       </c>
       <c r="B599" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="600">
@@ -7075,7 +7018,7 @@
         <v>600</v>
       </c>
       <c r="B600" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="601">
@@ -7083,7 +7026,7 @@
         <v>601</v>
       </c>
       <c r="B601" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="602">
@@ -7099,7 +7042,7 @@
         <v>603</v>
       </c>
       <c r="B603" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="604">
@@ -7115,7 +7058,7 @@
         <v>605</v>
       </c>
       <c r="B605" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="606">
@@ -7123,7 +7066,7 @@
         <v>606</v>
       </c>
       <c r="B606" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="607">
@@ -7139,7 +7082,7 @@
         <v>608</v>
       </c>
       <c r="B608" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="609">
@@ -7147,7 +7090,7 @@
         <v>609</v>
       </c>
       <c r="B609" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="610">
@@ -7179,7 +7122,7 @@
         <v>613</v>
       </c>
       <c r="B613" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="614">
@@ -7227,7 +7170,7 @@
         <v>619</v>
       </c>
       <c r="B619" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="620">
@@ -7243,7 +7186,7 @@
         <v>621</v>
       </c>
       <c r="B621" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="622">
@@ -7259,7 +7202,7 @@
         <v>623</v>
       </c>
       <c r="B623" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="624">
@@ -7283,159 +7226,7 @@
         <v>626</v>
       </c>
       <c r="B626" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="627">
-      <c r="A627" t="s">
-        <v>627</v>
-      </c>
-      <c r="B627" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="628">
-      <c r="A628" t="s">
-        <v>628</v>
-      </c>
-      <c r="B628" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="629">
-      <c r="A629" t="s">
-        <v>629</v>
-      </c>
-      <c r="B629" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="630">
-      <c r="A630" t="s">
-        <v>630</v>
-      </c>
-      <c r="B630" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="631">
-      <c r="A631" t="s">
-        <v>631</v>
-      </c>
-      <c r="B631" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="632">
-      <c r="A632" t="s">
-        <v>632</v>
-      </c>
-      <c r="B632" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="633">
-      <c r="A633" t="s">
-        <v>633</v>
-      </c>
-      <c r="B633" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="634">
-      <c r="A634" t="s">
-        <v>634</v>
-      </c>
-      <c r="B634" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="635">
-      <c r="A635" t="s">
-        <v>635</v>
-      </c>
-      <c r="B635" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="636">
-      <c r="A636" t="s">
-        <v>636</v>
-      </c>
-      <c r="B636" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="637">
-      <c r="A637" t="s">
-        <v>637</v>
-      </c>
-      <c r="B637" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="638">
-      <c r="A638" t="s">
-        <v>638</v>
-      </c>
-      <c r="B638" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="639">
-      <c r="A639" t="s">
-        <v>639</v>
-      </c>
-      <c r="B639" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="640">
-      <c r="A640" t="s">
-        <v>640</v>
-      </c>
-      <c r="B640" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="641">
-      <c r="A641" t="s">
-        <v>641</v>
-      </c>
-      <c r="B641" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="642">
-      <c r="A642" t="s">
-        <v>642</v>
-      </c>
-      <c r="B642" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="643">
-      <c r="A643" t="s">
-        <v>643</v>
-      </c>
-      <c r="B643" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="644">
-      <c r="A644" t="s">
-        <v>644</v>
-      </c>
-      <c r="B644" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="645">
-      <c r="A645" t="s">
-        <v>645</v>
-      </c>
-      <c r="B645" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
